--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -65180,13 +65180,13 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O359" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="R359" t="n">
-        <v>0.802319548449907</v>
+        <v>0.8061954882974911</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
@@ -65689,12 +65689,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65728,81 +65728,100 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O362" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R362" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP362" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR362" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS362" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU362" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -65829,17 +65848,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -65864,7 +65883,7 @@
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -65873,81 +65892,175 @@
         </is>
       </c>
       <c r="N363" t="n">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="O363" t="n">
-        <v>94</v>
-      </c>
-      <c r="R363" t="n">
-        <v>0.07677999031118203</v>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X363" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y363" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC363" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD363" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE363" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF363" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI363" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ363" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM363" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN363" t="b">
+        <v>1</v>
       </c>
       <c r="AO363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP363" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ363" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR363" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -65979,12 +66092,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -66009,7 +66122,7 @@
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -66018,93 +66131,81 @@
         </is>
       </c>
       <c r="N364" t="n">
+        <v>1</v>
+      </c>
+      <c r="O364" t="n">
+        <v>1</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR364" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr"/>
+      <c r="AT364" t="n">
         <v>0</v>
       </c>
-      <c r="O364" t="n">
-        <v>0</v>
-      </c>
-      <c r="P364" t="n">
-        <v>0</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO364" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP364" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ364" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT364" t="n">
-        <v>2</v>
-      </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66131,17 +66232,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -66175,173 +66276,81 @@
         </is>
       </c>
       <c r="N365" t="n">
+        <v>94</v>
+      </c>
+      <c r="O365" t="n">
+        <v>94</v>
+      </c>
+      <c r="R365" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr"/>
+      <c r="AT365" t="n">
         <v>0</v>
       </c>
-      <c r="O365" t="n">
-        <v>0</v>
-      </c>
-      <c r="P365" t="n">
-        <v>0</v>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W365" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X365" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y365" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA365" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB365" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC365" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD365" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE365" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF365" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI365" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ365" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK365" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM365" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN365" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO365" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP365" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ365" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS365" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT365" t="n">
-        <v>2</v>
-      </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66373,12 +66382,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66403,7 +66412,7 @@
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -66412,81 +66421,93 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P366" t="n">
+        <v>0</v>
       </c>
       <c r="R366" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S366" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA366" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR366" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ366" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT366" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66513,17 +66534,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66548,7 +66569,7 @@
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -66557,81 +66578,173 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="O367" t="n">
-        <v>73</v>
-      </c>
-      <c r="R367" t="n">
-        <v>0.05962701375230094</v>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P367" t="n">
+        <v>0</v>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN367" t="b">
+        <v>1</v>
       </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR367" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66663,12 +66776,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66693,7 +66806,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66702,93 +66815,81 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O368" t="n">
-        <v>4</v>
-      </c>
-      <c r="P368" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R368" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S368" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA368" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ368" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR368" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr"/>
       <c r="AT368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66815,17 +66916,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66859,173 +66960,81 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O369" t="n">
-        <v>4</v>
-      </c>
-      <c r="P369" t="n">
-        <v>4</v>
-      </c>
-      <c r="U369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W369" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X369" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y369" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA369" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB369" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC369" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD369" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE369" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF369" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG369" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH369" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI369" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ369" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK369" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM369" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN369" t="b">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="R369" t="n">
+        <v>0.05962701375230094</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ369" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr"/>
       <c r="AT369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67057,12 +67066,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -67087,7 +67096,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -67096,81 +67105,93 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="O370" t="n">
-        <v>64</v>
+        <v>4</v>
+      </c>
+      <c r="P370" t="n">
+        <v>4</v>
       </c>
       <c r="R370" t="n">
-        <v>0.05227573808420904</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA370" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR370" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ370" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT370" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67197,7 +67218,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -67232,7 +67253,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -67241,26 +67262,106 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P371" t="n">
-        <v>3</v>
-      </c>
-      <c r="R371" t="n">
-        <v>0.05079797265291142</v>
-      </c>
-      <c r="S371" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>4</v>
+      </c>
+      <c r="U371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W371" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X371" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y371" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB371" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC371" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD371" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE371" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF371" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG371" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH371" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI371" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ371" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK371" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM371" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN371" t="b">
+        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
@@ -67354,17 +67455,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -67398,173 +67499,81 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O372" t="n">
-        <v>3</v>
-      </c>
-      <c r="P372" t="n">
-        <v>3</v>
-      </c>
-      <c r="U372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA372" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD372" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE372" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG372" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ372" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK372" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM372" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN372" t="b">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="R372" t="n">
+        <v>0.05227573808420904</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ372" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR372" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr"/>
       <c r="AT372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67596,12 +67605,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67626,7 +67635,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -67635,81 +67644,93 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="O373" t="n">
-        <v>91</v>
+        <v>3</v>
+      </c>
+      <c r="P373" t="n">
+        <v>3</v>
       </c>
       <c r="R373" t="n">
-        <v>0.07432956508848473</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ373" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67736,7 +67757,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -67771,7 +67792,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -67780,26 +67801,106 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O374" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P374" t="n">
-        <v>4</v>
-      </c>
-      <c r="R374" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S374" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X374" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z374" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC374" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD374" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE374" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF374" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG374" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH374" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI374" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ374" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK374" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM374" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN374" t="b">
+        <v>1</v>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
@@ -67893,17 +67994,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -67937,173 +68038,81 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="O375" t="n">
-        <v>4</v>
-      </c>
-      <c r="P375" t="n">
-        <v>4</v>
-      </c>
-      <c r="U375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W375" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X375" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y375" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC375" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD375" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE375" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF375" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG375" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH375" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI375" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ375" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK375" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM375" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN375" t="b">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="R375" t="n">
+        <v>0.07432956508848473</v>
+      </c>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ375" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr"/>
       <c r="AT375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68135,12 +68144,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -68165,90 +68174,102 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N376" t="n">
+        <v>4</v>
+      </c>
+      <c r="O376" t="n">
+        <v>4</v>
+      </c>
+      <c r="P376" t="n">
+        <v>4</v>
+      </c>
+      <c r="R376" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA376" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO376" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP376" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ376" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT376" t="n">
         <v>2</v>
       </c>
-      <c r="O376" t="n">
-        <v>2</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO376" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP376" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR376" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr"/>
-      <c r="AT376" t="n">
-        <v>0</v>
-      </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68275,17 +68296,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -68310,37 +68331,115 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N377" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O377" t="n">
-        <v>0</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P377" t="n">
+        <v>4</v>
       </c>
       <c r="U377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
@@ -68349,22 +68448,17 @@
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ377" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR377" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS377" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
         </is>
       </c>
       <c r="AT377" t="n">
@@ -68372,47 +68466,47 @@
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68439,17 +68533,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68483,175 +68577,81 @@
         </is>
       </c>
       <c r="N378" t="n">
+        <v>2</v>
+      </c>
+      <c r="O378" t="n">
+        <v>2</v>
+      </c>
+      <c r="R378" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP378" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
+      <c r="AT378" t="n">
         <v>0</v>
       </c>
-      <c r="O378" t="n">
-        <v>0</v>
-      </c>
-      <c r="U378" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W378" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X378" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y378" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z378" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB378" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC378" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD378" t="inlineStr">
+      <c r="AU378" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV378" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE378" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF378" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG378" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH378" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI378" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ378" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK378" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM378" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN378" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO378" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP378" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT378" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU378" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV378" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -68683,12 +68683,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -68722,81 +68722,100 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O379" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="R379" t="n">
-        <v>0.04844924809480115</v>
+        <v>0</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO379" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP379" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ379" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR379" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS379" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT379" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68823,17 +68842,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68872,17 +68891,34 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="R380" t="n">
-        <v>0</v>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U380" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -68890,6 +68926,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
+      </c>
       <c r="AO380" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -68902,7 +68996,7 @@
       </c>
       <c r="AQ380" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR380" t="inlineStr">
@@ -68912,7 +69006,7 @@
       </c>
       <c r="AS380" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT380" t="n">
@@ -68920,47 +69014,47 @@
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -68987,217 +69081,526 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N381" t="n">
+        <v>36</v>
+      </c>
+      <c r="O381" t="n">
+        <v>36</v>
+      </c>
+      <c r="R381" t="n">
+        <v>0.06976691725651366</v>
+      </c>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP381" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
+      <c r="AT381" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU381" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV381" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW381" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX381" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY381" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA381" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB381" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC381" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N382" t="n">
+        <v>0</v>
+      </c>
+      <c r="O382" t="n">
+        <v>0</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO382" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP382" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ382" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT382" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU382" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV382" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW382" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX382" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY382" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA382" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB382" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC382" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F381" t="inlineStr">
+      <c r="F383" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr">
+      <c r="G383" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>D039</t>
-        </is>
-      </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
         <is>
           <t>流行性腮腺炎</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr">
+      <c r="K383" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L381" t="inlineStr">
+      <c r="L383" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M381" t="inlineStr">
+      <c r="M383" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N381" t="n">
+      <c r="N383" t="n">
         <v>0</v>
       </c>
-      <c r="O381" t="n">
+      <c r="O383" t="n">
         <v>0</v>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="U383" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
+      <c r="V383" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="W381" t="inlineStr">
+      <c r="W383" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X381" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>Kusma</t>
         </is>
       </c>
-      <c r="Y381" t="inlineStr">
+      <c r="Y383" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z381" t="inlineStr">
+      <c r="Z383" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA381" t="inlineStr">
+      <c r="AA383" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB381" t="inlineStr">
+      <c r="AB383" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC381" t="inlineStr">
+      <c r="AC383" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD381" t="inlineStr">
+      <c r="AD383" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE381" t="inlineStr">
+      <c r="AE383" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF381" t="inlineStr">
+      <c r="AF383" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG381" t="inlineStr">
+      <c r="AG383" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH381" t="inlineStr">
+      <c r="AH383" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI381" t="inlineStr">
+      <c r="AI383" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ381" t="inlineStr">
+      <c r="AJ383" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK381" t="inlineStr">
+      <c r="AK383" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM381" t="inlineStr">
+      <c r="AM383" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN381" t="b">
+      <c r="AN383" t="b">
         <v>1</v>
       </c>
-      <c r="AO381" t="inlineStr">
+      <c r="AO383" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP381" t="inlineStr">
+      <c r="AP383" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ381" t="inlineStr">
+      <c r="AQ383" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR381" t="inlineStr">
+      <c r="AR383" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS381" t="inlineStr">
+      <c r="AS383" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="AT381" t="n">
+      <c r="AT383" t="n">
         <v>2</v>
       </c>
-      <c r="AU381" t="inlineStr">
+      <c r="AU383" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV381" t="inlineStr">
+      <c r="AV383" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW381" t="inlineStr">
+      <c r="AW383" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX381" t="inlineStr">
+      <c r="AX383" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY381" t="inlineStr">
+      <c r="AY383" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ381" t="inlineStr">
+      <c r="AZ383" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA381" t="inlineStr">
+      <c r="BA383" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB381" t="inlineStr">
+      <c r="BB383" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC381" t="inlineStr">
+      <c r="BC383" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -69319,7 +69722,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -69329,7 +69732,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11">
@@ -69349,7 +69752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -69381,7 +69784,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67122</v>
+        <v>67138</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -63780,13 +63780,13 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O350" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R350" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
@@ -68538,12 +68538,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68568,22 +68568,22 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N378" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="O378" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="R378" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.08984892483223429</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -68616,42 +68616,42 @@
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68683,12 +68683,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -68722,100 +68722,81 @@
         </is>
       </c>
       <c r="N379" t="n">
+        <v>2</v>
+      </c>
+      <c r="O379" t="n">
+        <v>2</v>
+      </c>
+      <c r="R379" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO379" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP379" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR379" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS379" t="inlineStr"/>
+      <c r="AT379" t="n">
         <v>0</v>
       </c>
-      <c r="O379" t="n">
-        <v>0</v>
-      </c>
-      <c r="R379" t="n">
-        <v>0</v>
-      </c>
-      <c r="S379" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA379" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO379" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP379" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ379" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR379" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS379" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT379" t="n">
-        <v>2</v>
-      </c>
       <c r="AU379" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -68842,7 +68823,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -68891,98 +68872,23 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
+      <c r="R380" t="n">
+        <v>0</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U380" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W380" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y380" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA380" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB380" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC380" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD380" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE380" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG380" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ380" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK380" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM380" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN380" t="b">
-        <v>1</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
@@ -69081,17 +68987,17 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -69125,81 +69031,175 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O381" t="n">
-        <v>36</v>
-      </c>
-      <c r="R381" t="n">
-        <v>0.06976691725651366</v>
-      </c>
-      <c r="S381" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC381" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF381" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG381" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH381" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI381" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ381" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM381" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN381" t="b">
+        <v>1</v>
       </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ381" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR381" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -69231,12 +69231,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -69270,100 +69270,81 @@
         </is>
       </c>
       <c r="N382" t="n">
+        <v>36</v>
+      </c>
+      <c r="O382" t="n">
+        <v>36</v>
+      </c>
+      <c r="R382" t="n">
+        <v>0.06976691725651366</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP382" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR382" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS382" t="inlineStr"/>
+      <c r="AT382" t="n">
         <v>0</v>
       </c>
-      <c r="O382" t="n">
-        <v>0</v>
-      </c>
-      <c r="R382" t="n">
-        <v>0</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U382" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA382" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO382" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP382" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ382" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR382" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS382" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT382" t="n">
-        <v>2</v>
-      </c>
       <c r="AU382" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -69390,7 +69371,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -69439,98 +69420,23 @@
       <c r="O383" t="n">
         <v>0</v>
       </c>
+      <c r="R383" t="n">
+        <v>0</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U383" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X383" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y383" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA383" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC383" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD383" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE383" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG383" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH383" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI383" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ383" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK383" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM383" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN383" t="b">
-        <v>1</v>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
@@ -69601,6 +69507,245 @@
         </is>
       </c>
       <c r="BC383" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N384" t="n">
+        <v>0</v>
+      </c>
+      <c r="O384" t="n">
+        <v>0</v>
+      </c>
+      <c r="U384" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF384" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG384" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH384" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI384" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ384" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK384" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM384" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN384" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO384" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP384" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ384" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT384" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU384" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -69722,7 +69867,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -69732,7 +69877,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11">
@@ -69784,7 +69929,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67138</v>
+        <v>67249</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -65180,13 +65180,13 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O359" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="R359" t="n">
-        <v>0.8061954882974911</v>
+        <v>0.8081334582212831</v>
       </c>
       <c r="S359" t="inlineStr">
         <is>
@@ -69270,13 +69270,13 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="O382" t="n">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="R382" t="n">
-        <v>0.06976691725651366</v>
+        <v>0.1879830826078285</v>
       </c>
       <c r="S382" t="inlineStr">
         <is>
@@ -69929,7 +69929,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67249</v>
+        <v>67311</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -64738,12 +64738,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -64777,100 +64777,84 @@
         </is>
       </c>
       <c r="N357" t="n">
-        <v>2</v>
+        <v>5362</v>
       </c>
       <c r="O357" t="n">
-        <v>2</v>
+        <v>5362</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>0</v>
       </c>
       <c r="R357" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.3794993654350556</v>
       </c>
       <c r="S357" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA357" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO357" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP357" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ357" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR357" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS357" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
       <c r="AT357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU357" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV357" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW357" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX357" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY357" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ357" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA357" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB357" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC357" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -64897,7 +64881,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -64946,98 +64930,23 @@
       <c r="O358" t="n">
         <v>2</v>
       </c>
+      <c r="R358" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U358" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V358" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W358" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X358" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y358" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA358" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC358" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD358" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE358" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF358" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI358" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ358" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK358" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM358" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN358" t="b">
-        <v>1</v>
       </c>
       <c r="AO358" t="inlineStr">
         <is>
@@ -65136,17 +65045,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -65180,81 +65089,175 @@
         </is>
       </c>
       <c r="N359" t="n">
-        <v>417</v>
+        <v>2</v>
       </c>
       <c r="O359" t="n">
-        <v>417</v>
-      </c>
-      <c r="R359" t="n">
-        <v>0.8081334582212831</v>
-      </c>
-      <c r="S359" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W359" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X359" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y359" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB359" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC359" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD359" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE359" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF359" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI359" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ359" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM359" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN359" t="b">
+        <v>1</v>
       </c>
       <c r="AO359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP359" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ359" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR359" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS359" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU359" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV359" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW359" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX359" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY359" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ359" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA359" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB359" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC359" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -65286,12 +65289,12 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -65325,100 +65328,81 @@
         </is>
       </c>
       <c r="N360" t="n">
+        <v>417</v>
+      </c>
+      <c r="O360" t="n">
+        <v>417</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0.8081334582212831</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr"/>
+      <c r="AT360" t="n">
         <v>0</v>
       </c>
-      <c r="O360" t="n">
-        <v>0</v>
-      </c>
-      <c r="R360" t="n">
-        <v>0</v>
-      </c>
-      <c r="S360" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA360" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO360" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP360" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ360" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR360" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS360" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT360" t="n">
-        <v>2</v>
-      </c>
       <c r="AU360" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV360" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW360" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ360" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA360" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB360" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC360" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -65445,7 +65429,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -65494,98 +65478,23 @@
       <c r="O361" t="n">
         <v>0</v>
       </c>
+      <c r="R361" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U361" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V361" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W361" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X361" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y361" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA361" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB361" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC361" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD361" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE361" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF361" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI361" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ361" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK361" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM361" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN361" t="b">
-        <v>1</v>
       </c>
       <c r="AO361" t="inlineStr">
         <is>
@@ -65684,17 +65593,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65728,22 +65637,39 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O362" t="n">
-        <v>3</v>
-      </c>
-      <c r="R362" t="n">
-        <v>0.02803464128485004</v>
-      </c>
-      <c r="S362" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U362" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -65751,6 +65677,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM362" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN362" t="b">
+        <v>1</v>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -65773,7 +65757,7 @@
       </c>
       <c r="AS362" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT362" t="n">
@@ -65786,42 +65770,42 @@
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -65848,7 +65832,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -65897,98 +65881,23 @@
       <c r="O363" t="n">
         <v>3</v>
       </c>
+      <c r="R363" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U363" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MUMPS</t>
         </is>
       </c>
-      <c r="V363" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X363" t="inlineStr">
-        <is>
-          <t>Påssjuka</t>
-        </is>
-      </c>
-      <c r="Y363" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA363" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB363" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC363" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD363" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE363" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF363" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI363" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ363" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK363" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM363" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN363" t="b">
-        <v>1</v>
       </c>
       <c r="AO363" t="inlineStr">
         <is>
@@ -66087,17 +65996,17 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -66131,81 +66040,175 @@
         </is>
       </c>
       <c r="N364" t="n">
+        <v>3</v>
+      </c>
+      <c r="O364" t="n">
+        <v>3</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X364" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y364" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC364" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD364" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE364" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF364" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI364" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ364" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM364" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN364" t="b">
         <v>1</v>
       </c>
-      <c r="O364" t="n">
-        <v>1</v>
-      </c>
-      <c r="R364" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S364" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP364" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR364" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS364" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU364" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV364" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW364" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX364" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY364" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ364" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA364" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB364" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC364" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66237,12 +66240,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -66267,7 +66270,7 @@
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -66276,13 +66279,13 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="O365" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="R365" t="n">
-        <v>0.07677999031118203</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -66315,42 +66318,42 @@
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -66382,12 +66385,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66421,93 +66424,81 @@
         </is>
       </c>
       <c r="N366" t="n">
+        <v>94</v>
+      </c>
+      <c r="O366" t="n">
+        <v>94</v>
+      </c>
+      <c r="R366" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO366" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP366" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR366" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS366" t="inlineStr"/>
+      <c r="AT366" t="n">
         <v>0</v>
       </c>
-      <c r="O366" t="n">
-        <v>0</v>
-      </c>
-      <c r="P366" t="n">
-        <v>0</v>
-      </c>
-      <c r="R366" t="n">
-        <v>0</v>
-      </c>
-      <c r="S366" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA366" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO366" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP366" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ366" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS366" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT366" t="n">
-        <v>2</v>
-      </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66534,7 +66525,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -66586,98 +66577,18 @@
       <c r="P367" t="n">
         <v>0</v>
       </c>
-      <c r="U367" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V367" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W367" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X367" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y367" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R367" t="n">
+        <v>0</v>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB367" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC367" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD367" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE367" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF367" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG367" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH367" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI367" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ367" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK367" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM367" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN367" t="b">
-        <v>1</v>
       </c>
       <c r="AO367" t="inlineStr">
         <is>
@@ -66771,17 +66682,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66806,7 +66717,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66815,81 +66726,173 @@
         </is>
       </c>
       <c r="N368" t="n">
+        <v>0</v>
+      </c>
+      <c r="O368" t="n">
+        <v>0</v>
+      </c>
+      <c r="P368" t="n">
+        <v>0</v>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN368" t="b">
         <v>1</v>
       </c>
-      <c r="O368" t="n">
-        <v>1</v>
-      </c>
-      <c r="R368" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR368" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -66921,12 +66924,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66951,7 +66954,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -66960,13 +66963,13 @@
         </is>
       </c>
       <c r="N369" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O369" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R369" t="n">
-        <v>0.05962701375230094</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S369" t="inlineStr">
         <is>
@@ -66999,42 +67002,42 @@
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67066,12 +67069,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -67105,93 +67108,81 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O370" t="n">
-        <v>4</v>
-      </c>
-      <c r="P370" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="R370" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.05962701375230094</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO370" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP370" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
       <c r="AT370" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67218,7 +67209,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -67270,98 +67261,18 @@
       <c r="P371" t="n">
         <v>4</v>
       </c>
-      <c r="U371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W371" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X371" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y371" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R371" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB371" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC371" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD371" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE371" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF371" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG371" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH371" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI371" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ371" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK371" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM371" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN371" t="b">
-        <v>1</v>
       </c>
       <c r="AO371" t="inlineStr">
         <is>
@@ -67455,17 +67366,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -67490,7 +67401,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -67499,81 +67410,173 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="O372" t="n">
-        <v>64</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0.05227573808420904</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P372" t="n">
+        <v>4</v>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR372" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67605,12 +67608,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67644,93 +67647,81 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O373" t="n">
-        <v>3</v>
-      </c>
-      <c r="P373" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="R373" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.05227573808420904</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA373" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ373" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr"/>
       <c r="AT373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67757,7 +67748,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -67809,98 +67800,18 @@
       <c r="P374" t="n">
         <v>3</v>
       </c>
-      <c r="U374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X374" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y374" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R374" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC374" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE374" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG374" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ374" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK374" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM374" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN374" t="b">
-        <v>1</v>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
@@ -67994,17 +67905,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -68029,7 +67940,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -68038,81 +67949,173 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="O375" t="n">
-        <v>91</v>
-      </c>
-      <c r="R375" t="n">
-        <v>0.07432956508848473</v>
-      </c>
-      <c r="S375" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P375" t="n">
+        <v>3</v>
+      </c>
+      <c r="U375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W375" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X375" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y375" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC375" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD375" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE375" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF375" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG375" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH375" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI375" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ375" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM375" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN375" t="b">
+        <v>1</v>
       </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR375" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68144,12 +68147,12 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
@@ -68183,93 +68186,81 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="O376" t="n">
-        <v>4</v>
-      </c>
-      <c r="P376" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="R376" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.07432956508848473</v>
       </c>
       <c r="S376" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA376" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO376" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP376" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ376" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR376" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS376" t="inlineStr"/>
       <c r="AT376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU376" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ376" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA376" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB376" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC376" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68296,7 +68287,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -68348,98 +68339,18 @@
       <c r="P377" t="n">
         <v>4</v>
       </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R377" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG377" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ377" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK377" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM377" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN377" t="b">
-        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
@@ -68533,17 +68444,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68568,7 +68479,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -68577,81 +68488,173 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="O378" t="n">
-        <v>110</v>
-      </c>
-      <c r="R378" t="n">
-        <v>0.08984892483223429</v>
-      </c>
-      <c r="S378" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P378" t="n">
+        <v>4</v>
+      </c>
+      <c r="U378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB378" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC378" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF378" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG378" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH378" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI378" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ378" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM378" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN378" t="b">
+        <v>1</v>
       </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68683,12 +68686,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -68713,22 +68716,22 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N379" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="O379" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="R379" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.08984892483223429</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -68761,42 +68764,42 @@
       </c>
       <c r="AV379" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW379" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX379" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY379" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ379" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA379" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB379" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC379" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68828,12 +68831,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68858,36 +68861,34 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O380" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P380" t="n">
+        <v>2</v>
       </c>
       <c r="R380" t="n">
-        <v>0</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S380" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
       <c r="AA380" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO380" t="inlineStr">
@@ -68897,22 +68898,17 @@
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ380" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS380" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
         </is>
       </c>
       <c r="AT380" t="n">
@@ -68920,47 +68916,47 @@
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68992,12 +68988,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -69022,38 +69018,41 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O381" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P381" t="n">
+        <v>2</v>
       </c>
       <c r="U381" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS</t>
         </is>
       </c>
       <c r="V381" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS</t>
         </is>
       </c>
       <c r="W381" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X381" t="inlineStr">
         <is>
-          <t>Swine fever</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="Y381" t="inlineStr">
@@ -69063,12 +69062,12 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB381" t="inlineStr">
@@ -69078,7 +69077,7 @@
       </c>
       <c r="AC381" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD381" t="inlineStr">
@@ -69113,12 +69112,12 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM381" t="inlineStr">
@@ -69136,22 +69135,17 @@
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ381" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR381" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS381" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
         </is>
       </c>
       <c r="AT381" t="n">
@@ -69159,47 +69153,47 @@
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69231,12 +69225,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -69270,13 +69264,13 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="O382" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="R382" t="n">
-        <v>0.1879830826078285</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S382" t="inlineStr">
         <is>
@@ -69309,42 +69303,42 @@
       </c>
       <c r="AV382" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW382" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX382" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY382" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ382" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA382" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB382" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC382" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -69376,12 +69370,12 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -69430,7 +69424,7 @@
       </c>
       <c r="U383" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -69450,7 +69444,7 @@
       </c>
       <c r="AQ383" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR383" t="inlineStr">
@@ -69460,7 +69454,7 @@
       </c>
       <c r="AS383" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT383" t="n">
@@ -69468,47 +69462,47 @@
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -69540,12 +69534,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -69586,22 +69580,22 @@
       </c>
       <c r="U384" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="V384" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="W384" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X384" t="inlineStr">
         <is>
-          <t>Kusma</t>
+          <t>Swine fever</t>
         </is>
       </c>
       <c r="Y384" t="inlineStr">
@@ -69626,7 +69620,7 @@
       </c>
       <c r="AC384" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD384" t="inlineStr">
@@ -69661,17 +69655,17 @@
       </c>
       <c r="AJ384" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK384" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
         </is>
       </c>
       <c r="AM384" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN384" t="b">
@@ -69689,7 +69683,7 @@
       </c>
       <c r="AQ384" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR384" t="inlineStr">
@@ -69699,7 +69693,7 @@
       </c>
       <c r="AS384" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT384" t="n">
@@ -69707,47 +69701,740 @@
       </c>
       <c r="AU384" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV384" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW384" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX384" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY384" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA384" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB384" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC384" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N385" t="n">
+        <v>97</v>
+      </c>
+      <c r="O385" t="n">
+        <v>97</v>
+      </c>
+      <c r="R385" t="n">
+        <v>0.1879830826078285</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP385" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR385" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS385" t="inlineStr"/>
+      <c r="AT385" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU385" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV385" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW385" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX385" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY385" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA385" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB385" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC385" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>0</v>
+      </c>
+      <c r="O386" t="n">
+        <v>0</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ386" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT386" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU386" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV384" t="inlineStr">
+      <c r="AV386" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW384" t="inlineStr">
+      <c r="AW386" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX384" t="inlineStr">
+      <c r="AX386" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY384" t="inlineStr">
+      <c r="AY386" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ384" t="inlineStr">
+      <c r="AZ386" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA384" t="inlineStr">
+      <c r="BA386" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB384" t="inlineStr">
+      <c r="BB386" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC384" t="inlineStr">
+      <c r="BC386" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>0</v>
+      </c>
+      <c r="O387" t="n">
+        <v>0</v>
+      </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF387" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG387" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH387" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI387" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ387" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK387" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM387" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN387" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO387" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP387" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ387" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR387" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT387" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU387" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV387" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW387" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX387" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY387" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA387" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB387" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC387" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>1</v>
+      </c>
+      <c r="O388" t="n">
+        <v>1</v>
+      </c>
+      <c r="R388" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO388" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP388" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR388" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS388" t="inlineStr"/>
+      <c r="AT388" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU388" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV388" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW388" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX388" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY388" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA388" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB388" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC388" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -69784,7 +70471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -69867,7 +70554,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -69877,7 +70564,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11">
@@ -69897,7 +70584,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -69929,7 +70616,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67311</v>
+        <v>72676</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -64170,13 +64170,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O352" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R352" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.02203687091711874</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -65718,13 +65718,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O362" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R362" t="n">
-        <v>0.8081334582212831</v>
+        <v>0.8100714281450753</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -70202,13 +70202,13 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="O387" t="n">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="R387" t="n">
-        <v>0.1879830826078285</v>
+        <v>0.2325563908550455</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -71006,7 +71006,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72678</v>
+        <v>72703</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -65718,13 +65718,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="O362" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R362" t="n">
-        <v>0.8100714281450753</v>
+        <v>0.8081334582212831</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -70202,13 +70202,13 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="O387" t="n">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="R387" t="n">
-        <v>0.2325563908550455</v>
+        <v>0.3081372178829353</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
@@ -70825,6 +70825,151 @@
       <c r="BC390" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>72</v>
+      </c>
+      <c r="O391" t="n">
+        <v>72</v>
+      </c>
+      <c r="R391" t="n">
+        <v>0.05881020534473518</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR391" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr"/>
+      <c r="AT391" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV391" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW391" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX391" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY391" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA391" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB391" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC391" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -70861,7 +71006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -70944,7 +71089,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -70954,7 +71099,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -71006,7 +71151,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72703</v>
+        <v>72813</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -66227,12 +66227,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -66266,13 +66266,13 @@
         </is>
       </c>
       <c r="N365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R365" t="n">
-        <v>0.02803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S365" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
       </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -66296,7 +66296,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ365" t="inlineStr">
@@ -66304,62 +66304,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR365" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS365" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66391,12 +66386,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -66430,29 +66425,29 @@
         </is>
       </c>
       <c r="N366" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U366" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="V366" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="W366" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X366" t="inlineStr">
         <is>
-          <t>Påssjuka</t>
+          <t>Mumps</t>
         </is>
       </c>
       <c r="Y366" t="inlineStr">
@@ -66462,7 +66457,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -66477,7 +66472,7 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD366" t="inlineStr">
@@ -66512,17 +66507,17 @@
       </c>
       <c r="AJ366" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK366" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly mumps notifications.</t>
         </is>
       </c>
       <c r="AM366" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN366" t="b">
@@ -66535,7 +66530,7 @@
       </c>
       <c r="AP366" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ366" t="inlineStr">
@@ -66543,62 +66538,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR366" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS366" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU366" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV366" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW366" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ366" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA366" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB366" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC366" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66630,12 +66620,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66669,81 +66659,100 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R367" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S367" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ367" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR367" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS367" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS367" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66770,17 +66779,17 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -66805,7 +66814,7 @@
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -66814,81 +66823,175 @@
         </is>
       </c>
       <c r="N368" t="n">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="O368" t="n">
-        <v>94</v>
-      </c>
-      <c r="R368" t="n">
-        <v>0.07677999031118203</v>
-      </c>
-      <c r="S368" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W368" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X368" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y368" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z368" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC368" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD368" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE368" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF368" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG368" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH368" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI368" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ368" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM368" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN368" t="b">
+        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP368" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ368" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR368" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS368" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS368" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU368" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ368" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA368" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB368" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC368" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -66920,12 +67023,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -66950,7 +67053,7 @@
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -66959,93 +67062,81 @@
         </is>
       </c>
       <c r="N369" t="n">
+        <v>1</v>
+      </c>
+      <c r="O369" t="n">
+        <v>1</v>
+      </c>
+      <c r="R369" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO369" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP369" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR369" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr"/>
+      <c r="AT369" t="n">
         <v>0</v>
       </c>
-      <c r="O369" t="n">
-        <v>0</v>
-      </c>
-      <c r="P369" t="n">
-        <v>0</v>
-      </c>
-      <c r="R369" t="n">
-        <v>0</v>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA369" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO369" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP369" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ369" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT369" t="n">
-        <v>2</v>
-      </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67072,17 +67163,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -67116,173 +67207,81 @@
         </is>
       </c>
       <c r="N370" t="n">
+        <v>94</v>
+      </c>
+      <c r="O370" t="n">
+        <v>94</v>
+      </c>
+      <c r="R370" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO370" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP370" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR370" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS370" t="inlineStr"/>
+      <c r="AT370" t="n">
         <v>0</v>
       </c>
-      <c r="O370" t="n">
-        <v>0</v>
-      </c>
-      <c r="P370" t="n">
-        <v>0</v>
-      </c>
-      <c r="U370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W370" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X370" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y370" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA370" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB370" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC370" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD370" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE370" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF370" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG370" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH370" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI370" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ370" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK370" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM370" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN370" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO370" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP370" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ370" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS370" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT370" t="n">
-        <v>2</v>
-      </c>
       <c r="AU370" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67314,12 +67313,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -67344,7 +67343,7 @@
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -67353,81 +67352,93 @@
         </is>
       </c>
       <c r="N371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O371" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P371" t="n">
+        <v>0</v>
       </c>
       <c r="R371" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S371" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA371" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP371" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR371" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ371" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT371" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67454,17 +67465,17 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -67489,7 +67500,7 @@
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -67498,81 +67509,173 @@
         </is>
       </c>
       <c r="N372" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="O372" t="n">
-        <v>73</v>
-      </c>
-      <c r="R372" t="n">
-        <v>0.05962701375230094</v>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P372" t="n">
+        <v>0</v>
+      </c>
+      <c r="U372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W372" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X372" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y372" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB372" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC372" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD372" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE372" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF372" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG372" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH372" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI372" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ372" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM372" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN372" t="b">
+        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP372" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR372" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS372" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ372" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS372" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU372" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV372" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW372" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX372" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY372" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ372" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA372" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB372" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC372" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67604,12 +67707,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67634,7 +67737,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -67643,93 +67746,81 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O373" t="n">
-        <v>4</v>
-      </c>
-      <c r="P373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R373" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA373" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ373" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR373" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr"/>
       <c r="AT373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67756,17 +67847,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67800,173 +67891,81 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O374" t="n">
-        <v>4</v>
-      </c>
-      <c r="P374" t="n">
-        <v>4</v>
-      </c>
-      <c r="U374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W374" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X374" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y374" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC374" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD374" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE374" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF374" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG374" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH374" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI374" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ374" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK374" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM374" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN374" t="b">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="R374" t="n">
+        <v>0.05962701375230094</v>
+      </c>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO374" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP374" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ374" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS374" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR374" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS374" t="inlineStr"/>
       <c r="AT374" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU374" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67998,12 +67997,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -68028,7 +68027,7 @@
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -68037,81 +68036,93 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="O375" t="n">
-        <v>64</v>
+        <v>4</v>
+      </c>
+      <c r="P375" t="n">
+        <v>4</v>
       </c>
       <c r="R375" t="n">
-        <v>0.05227573808420904</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR375" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ375" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68138,7 +68149,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -68173,7 +68184,7 @@
       </c>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
@@ -68182,26 +68193,106 @@
         </is>
       </c>
       <c r="N376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O376" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P376" t="n">
-        <v>3</v>
-      </c>
-      <c r="R376" t="n">
-        <v>0.05079797265291142</v>
-      </c>
-      <c r="S376" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>4</v>
+      </c>
+      <c r="U376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W376" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X376" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y376" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB376" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC376" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD376" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE376" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF376" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG376" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH376" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI376" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ376" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM376" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN376" t="b">
+        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
@@ -68295,17 +68386,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -68339,173 +68430,81 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O377" t="n">
-        <v>3</v>
-      </c>
-      <c r="P377" t="n">
-        <v>3</v>
-      </c>
-      <c r="U377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W377" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X377" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y377" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z377" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA377" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB377" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC377" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD377" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE377" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF377" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG377" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH377" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI377" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ377" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK377" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM377" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN377" t="b">
-        <v>1</v>
+        <v>64</v>
+      </c>
+      <c r="R377" t="n">
+        <v>0.05227573808420904</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ377" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR377" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr"/>
       <c r="AT377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68537,12 +68536,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68567,7 +68566,7 @@
       </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
@@ -68576,81 +68575,93 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="O378" t="n">
-        <v>91</v>
+        <v>3</v>
+      </c>
+      <c r="P378" t="n">
+        <v>3</v>
       </c>
       <c r="R378" t="n">
-        <v>0.07432956508848473</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR378" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ378" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68677,7 +68688,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -68712,7 +68723,7 @@
       </c>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -68721,26 +68732,106 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O379" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P379" t="n">
-        <v>4</v>
-      </c>
-      <c r="R379" t="n">
-        <v>0.0677306302038819</v>
-      </c>
-      <c r="S379" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB379" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC379" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF379" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG379" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH379" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI379" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ379" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK379" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM379" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN379" t="b">
+        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -68834,17 +68925,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68878,173 +68969,81 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="O380" t="n">
-        <v>4</v>
-      </c>
-      <c r="P380" t="n">
-        <v>4</v>
-      </c>
-      <c r="U380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W380" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X380" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y380" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA380" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB380" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC380" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD380" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE380" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF380" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG380" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH380" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI380" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ380" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK380" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM380" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN380" t="b">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="R380" t="n">
+        <v>0.07432956508848473</v>
+      </c>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ380" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR380" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr"/>
       <c r="AT380" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69076,12 +69075,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -69106,7 +69105,7 @@
       </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
@@ -69115,81 +69114,93 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="O381" t="n">
-        <v>110</v>
+        <v>4</v>
+      </c>
+      <c r="P381" t="n">
+        <v>4</v>
       </c>
       <c r="R381" t="n">
-        <v>0.08984892483223429</v>
+        <v>0.0677306302038819</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR381" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ381" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT381" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69216,7 +69227,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -69251,7 +69262,7 @@
       </c>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
@@ -69260,26 +69271,106 @@
         </is>
       </c>
       <c r="N382" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O382" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P382" t="n">
-        <v>2</v>
-      </c>
-      <c r="R382" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>4</v>
+      </c>
+      <c r="U382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB382" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC382" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF382" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG382" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH382" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI382" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ382" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM382" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN382" t="b">
+        <v>1</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
@@ -69373,17 +69464,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -69417,173 +69508,81 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="O383" t="n">
-        <v>2</v>
-      </c>
-      <c r="P383" t="n">
-        <v>2</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W383" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X383" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y383" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z383" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC383" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD383" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE383" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF383" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG383" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH383" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI383" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ383" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK383" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM383" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN383" t="b">
-        <v>1</v>
+        <v>110</v>
+      </c>
+      <c r="R383" t="n">
+        <v>0.08984892483223429</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ383" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR383" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr"/>
       <c r="AT383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69615,12 +69614,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -69645,12 +69644,12 @@
       </c>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N384" t="n">
@@ -69659,76 +69658,88 @@
       <c r="O384" t="n">
         <v>2</v>
       </c>
+      <c r="P384" t="n">
+        <v>2</v>
+      </c>
       <c r="R384" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR384" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ384" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69755,17 +69766,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -69790,37 +69801,115 @@
       </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O385" t="n">
-        <v>0</v>
-      </c>
-      <c r="R385" t="n">
-        <v>0</v>
-      </c>
-      <c r="S385" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P385" t="n">
+        <v>2</v>
       </c>
       <c r="U385" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF385" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG385" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH385" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI385" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ385" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM385" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN385" t="b">
+        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -69829,22 +69918,17 @@
       </c>
       <c r="AP385" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ385" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR385" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS385" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_171</t>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
         </is>
       </c>
       <c r="AT385" t="n">
@@ -69852,47 +69936,47 @@
       </c>
       <c r="AU385" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV385" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW385" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX385" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY385" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ385" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA385" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB385" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC385" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69919,17 +70003,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -69963,175 +70047,81 @@
         </is>
       </c>
       <c r="N386" t="n">
+        <v>2</v>
+      </c>
+      <c r="O386" t="n">
+        <v>2</v>
+      </c>
+      <c r="R386" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP386" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR386" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr"/>
+      <c r="AT386" t="n">
         <v>0</v>
       </c>
-      <c r="O386" t="n">
-        <v>0</v>
-      </c>
-      <c r="U386" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W386" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X386" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y386" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z386" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA386" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB386" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC386" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD386" t="inlineStr">
+      <c r="AU386" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV386" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE386" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF386" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG386" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH386" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI386" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ386" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK386" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM386" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN386" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO386" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP386" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ386" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR386" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS386" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT386" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU386" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV386" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA386" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB386" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC386" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -70163,12 +70153,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -70202,81 +70192,100 @@
         </is>
       </c>
       <c r="N387" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="O387" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="R387" t="n">
-        <v>0.3081372178829353</v>
+        <v>0</v>
       </c>
       <c r="S387" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U387" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO387" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP387" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ387" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR387" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS387" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT387" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU387" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -70303,17 +70312,17 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -70352,17 +70361,34 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
-      <c r="R388" t="n">
-        <v>0</v>
-      </c>
-      <c r="S388" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U388" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -70370,6 +70396,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF388" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG388" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH388" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI388" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ388" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK388" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM388" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN388" t="b">
+        <v>1</v>
+      </c>
       <c r="AO388" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -70382,7 +70466,7 @@
       </c>
       <c r="AQ388" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR388" t="inlineStr">
@@ -70392,7 +70476,7 @@
       </c>
       <c r="AS388" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
+          <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
       <c r="AT388" t="n">
@@ -70400,47 +70484,47 @@
       </c>
       <c r="AU388" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV388" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW388" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX388" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY388" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ388" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA388" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB388" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC388" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -70467,17 +70551,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -70511,175 +70595,81 @@
         </is>
       </c>
       <c r="N389" t="n">
+        <v>178</v>
+      </c>
+      <c r="O389" t="n">
+        <v>178</v>
+      </c>
+      <c r="R389" t="n">
+        <v>0.3449586464349841</v>
+      </c>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO389" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP389" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR389" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr"/>
+      <c r="AT389" t="n">
         <v>0</v>
       </c>
-      <c r="O389" t="n">
-        <v>0</v>
-      </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W389" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X389" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y389" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z389" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA389" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC389" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD389" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE389" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF389" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG389" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH389" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI389" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ389" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK389" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM389" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN389" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO389" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP389" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ389" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR389" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS389" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT389" t="n">
-        <v>2</v>
-      </c>
       <c r="AU389" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA389" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB389" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC389" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -70711,12 +70701,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -70741,7 +70731,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -70750,81 +70740,100 @@
         </is>
       </c>
       <c r="N390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R390" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S390" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U390" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO390" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP390" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ390" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR390" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS390" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT390" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA390" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB390" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC390" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -70851,123 +70860,507 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>0</v>
+      </c>
+      <c r="O391" t="n">
+        <v>0</v>
+      </c>
+      <c r="U391" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z391" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF391" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG391" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH391" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI391" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ391" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK391" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM391" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN391" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO391" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP391" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ391" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR391" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS391" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT391" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU391" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV391" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW391" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX391" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY391" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA391" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB391" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC391" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F391" t="inlineStr">
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N392" t="n">
+        <v>1</v>
+      </c>
+      <c r="O392" t="n">
+        <v>1</v>
+      </c>
+      <c r="R392" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP392" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR392" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr"/>
+      <c r="AT392" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU392" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV392" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW392" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX392" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY392" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA392" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB392" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC392" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr">
+      <c r="G393" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>D039</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="J391" t="inlineStr">
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
         <is>
           <t>流行性腮腺炎</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr">
+      <c r="K393" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L391" t="inlineStr">
+      <c r="L393" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M391" t="inlineStr">
+      <c r="M393" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N391" t="n">
+      <c r="N393" t="n">
         <v>72</v>
       </c>
-      <c r="O391" t="n">
+      <c r="O393" t="n">
         <v>72</v>
       </c>
-      <c r="R391" t="n">
+      <c r="R393" t="n">
         <v>0.05881020534473518</v>
       </c>
-      <c r="S391" t="inlineStr">
+      <c r="S393" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO391" t="inlineStr">
+      <c r="AO393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP391" t="inlineStr">
+      <c r="AP393" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR391" t="inlineStr">
+      <c r="AR393" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS391" t="inlineStr"/>
-      <c r="AT391" t="n">
+      <c r="AS393" t="inlineStr"/>
+      <c r="AT393" t="n">
         <v>0</v>
       </c>
-      <c r="AU391" t="inlineStr">
+      <c r="AU393" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV391" t="inlineStr">
+      <c r="AV393" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW391" t="inlineStr">
+      <c r="AW393" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX391" t="inlineStr">
+      <c r="AX393" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY391" t="inlineStr">
+      <c r="AY393" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ391" t="inlineStr">
+      <c r="AZ393" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA391" t="inlineStr">
+      <c r="BA393" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB391" t="inlineStr">
+      <c r="BB393" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC391" t="inlineStr">
+      <c r="BC393" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -71089,7 +71482,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -71099,7 +71492,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="11">
@@ -71119,7 +71512,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -71151,7 +71544,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72813</v>
+        <v>72832</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -64170,13 +64170,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O352" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R352" t="n">
-        <v>0.02203687091711874</v>
+        <v>0.02938249455615832</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -70595,13 +70595,13 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="O389" t="n">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="R389" t="n">
-        <v>0.3449586464349841</v>
+        <v>0.4244154133104581</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
@@ -71363,6 +71363,400 @@
       <c r="BC393" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N394" t="n">
+        <v>2</v>
+      </c>
+      <c r="O394" t="n">
+        <v>2</v>
+      </c>
+      <c r="P394" t="n">
+        <v>2</v>
+      </c>
+      <c r="R394" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO394" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP394" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ394" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT394" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU394" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV394" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW394" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX394" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY394" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA394" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB394" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC394" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N395" t="n">
+        <v>2</v>
+      </c>
+      <c r="O395" t="n">
+        <v>2</v>
+      </c>
+      <c r="P395" t="n">
+        <v>2</v>
+      </c>
+      <c r="U395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB395" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC395" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF395" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG395" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH395" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI395" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ395" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK395" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM395" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN395" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO395" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP395" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ395" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS395" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT395" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU395" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV395" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW395" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX395" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY395" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA395" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB395" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC395" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -71482,7 +71876,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -71492,7 +71886,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
@@ -71512,7 +71906,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -71544,7 +71938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72832</v>
+        <v>72877</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -65718,13 +65718,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="O362" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="R362" t="n">
-        <v>0.8081334582212831</v>
+        <v>0.8158853379164512</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -70595,13 +70595,13 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="O389" t="n">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="R389" t="n">
-        <v>0.4244154133104581</v>
+        <v>0.5116240598811002</v>
       </c>
       <c r="S389" t="inlineStr">
         <is>
@@ -71938,7 +71938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72877</v>
+        <v>72926</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -54782,13 +54782,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O299" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R299" t="n">
-        <v>0.01469124727807916</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
@@ -65679,12 +65679,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -65718,13 +65718,13 @@
         </is>
       </c>
       <c r="N362" t="n">
-        <v>421</v>
+        <v>2</v>
       </c>
       <c r="O362" t="n">
-        <v>421</v>
+        <v>2</v>
       </c>
       <c r="R362" t="n">
-        <v>0.8158853379164512</v>
+        <v>0.02710540560393419</v>
       </c>
       <c r="S362" t="inlineStr">
         <is>
@@ -65757,42 +65757,42 @@
       </c>
       <c r="AV362" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ362" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA362" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB362" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC362" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -65824,12 +65824,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -65863,100 +65863,81 @@
         </is>
       </c>
       <c r="N363" t="n">
+        <v>423</v>
+      </c>
+      <c r="O363" t="n">
+        <v>423</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0.8197612777640354</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="n">
         <v>0</v>
       </c>
-      <c r="O363" t="n">
-        <v>0</v>
-      </c>
-      <c r="R363" t="n">
-        <v>0</v>
-      </c>
-      <c r="S363" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA363" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO363" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP363" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ363" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR363" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS363" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT363" t="n">
-        <v>2</v>
-      </c>
       <c r="AU363" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV363" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ363" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA363" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB363" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC363" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -65983,7 +65964,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -66032,98 +66013,23 @@
       <c r="O364" t="n">
         <v>0</v>
       </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U364" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V364" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X364" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y364" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA364" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC364" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD364" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE364" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF364" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI364" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ364" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK364" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM364" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN364" t="b">
-        <v>1</v>
       </c>
       <c r="AO364" t="inlineStr">
         <is>
@@ -66222,17 +66128,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -66271,17 +66177,34 @@
       <c r="O365" t="n">
         <v>0</v>
       </c>
-      <c r="R365" t="n">
-        <v>0</v>
-      </c>
-      <c r="S365" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U365" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -66289,6 +66212,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
+      </c>
       <c r="AO365" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -66296,7 +66277,7 @@
       </c>
       <c r="AP365" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ365" t="inlineStr">
@@ -66304,57 +66285,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR365" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS365" t="inlineStr">
         <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
+          <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
       <c r="AT365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU365" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV365" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW365" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ365" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA365" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB365" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC365" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -66381,7 +66367,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -66430,98 +66416,23 @@
       <c r="O366" t="n">
         <v>0</v>
       </c>
+      <c r="R366" t="n">
+        <v>0</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U366" t="inlineStr">
         <is>
           <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
-      <c r="V366" t="inlineStr">
-        <is>
-          <t>SER_NZ_MUMPS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W366" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X366" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y366" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA366" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB366" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC366" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD366" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE366" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF366" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG366" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH366" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI366" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ366" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK366" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly mumps notifications.</t>
-        </is>
-      </c>
-      <c r="AM366" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN366" t="b">
-        <v>1</v>
       </c>
       <c r="AO366" t="inlineStr">
         <is>
@@ -66615,17 +66526,17 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -66659,22 +66570,39 @@
         </is>
       </c>
       <c r="N367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O367" t="n">
-        <v>3</v>
-      </c>
-      <c r="R367" t="n">
-        <v>0.02803464128485004</v>
-      </c>
-      <c r="S367" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U367" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W367" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X367" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y367" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z367" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -66682,6 +66610,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB367" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC367" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD367" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE367" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF367" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG367" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH367" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI367" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ367" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly mumps notifications.</t>
+        </is>
+      </c>
+      <c r="AM367" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN367" t="b">
+        <v>1</v>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -66689,7 +66675,7 @@
       </c>
       <c r="AP367" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ367" t="inlineStr">
@@ -66697,62 +66683,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR367" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS367" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+          <t>SER_NZ_MUMPS_MONTHLY</t>
         </is>
       </c>
       <c r="AT367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU367" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV367" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW367" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ367" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA367" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB367" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC367" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -66779,7 +66760,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -66828,98 +66809,23 @@
       <c r="O368" t="n">
         <v>3</v>
       </c>
+      <c r="R368" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U368" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_MUMPS</t>
         </is>
       </c>
-      <c r="V368" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_MUMPS</t>
-        </is>
-      </c>
-      <c r="W368" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X368" t="inlineStr">
-        <is>
-          <t>Påssjuka</t>
-        </is>
-      </c>
-      <c r="Y368" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA368" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC368" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD368" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE368" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF368" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG368" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH368" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI368" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ368" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK368" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM368" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN368" t="b">
-        <v>1</v>
       </c>
       <c r="AO368" t="inlineStr">
         <is>
@@ -67018,17 +66924,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -67062,81 +66968,175 @@
         </is>
       </c>
       <c r="N369" t="n">
+        <v>3</v>
+      </c>
+      <c r="O369" t="n">
+        <v>3</v>
+      </c>
+      <c r="U369" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
+      <c r="W369" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X369" t="inlineStr">
+        <is>
+          <t>Påssjuka</t>
+        </is>
+      </c>
+      <c r="Y369" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA369" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB369" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC369" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD369" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE369" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF369" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG369" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH369" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI369" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ369" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM369" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN369" t="b">
         <v>1</v>
       </c>
-      <c r="O369" t="n">
-        <v>1</v>
-      </c>
-      <c r="R369" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S369" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP369" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ369" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR369" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS369" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS369" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MUMPS</t>
+        </is>
+      </c>
       <c r="AT369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU369" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV369" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW369" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX369" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY369" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ369" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA369" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB369" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC369" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -67168,12 +67168,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -67198,7 +67198,7 @@
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -67207,13 +67207,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="O370" t="n">
-        <v>94</v>
+        <v>1</v>
       </c>
       <c r="R370" t="n">
-        <v>0.07677999031118203</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -67246,42 +67246,42 @@
       </c>
       <c r="AV370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ370" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA370" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB370" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC370" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67313,12 +67313,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -67352,93 +67352,81 @@
         </is>
       </c>
       <c r="N371" t="n">
+        <v>94</v>
+      </c>
+      <c r="O371" t="n">
+        <v>94</v>
+      </c>
+      <c r="R371" t="n">
+        <v>0.07677999031118203</v>
+      </c>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO371" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP371" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR371" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS371" t="inlineStr"/>
+      <c r="AT371" t="n">
         <v>0</v>
       </c>
-      <c r="O371" t="n">
-        <v>0</v>
-      </c>
-      <c r="P371" t="n">
-        <v>0</v>
-      </c>
-      <c r="R371" t="n">
-        <v>0</v>
-      </c>
-      <c r="S371" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA371" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO371" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP371" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ371" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS371" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
-      <c r="AT371" t="n">
-        <v>2</v>
-      </c>
       <c r="AU371" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ371" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA371" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB371" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC371" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -67465,7 +67453,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -67517,98 +67505,18 @@
       <c r="P372" t="n">
         <v>0</v>
       </c>
-      <c r="U372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V372" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W372" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X372" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y372" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R372" t="n">
+        <v>0</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB372" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC372" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD372" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE372" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF372" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG372" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH372" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI372" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ372" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK372" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM372" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN372" t="b">
-        <v>1</v>
       </c>
       <c r="AO372" t="inlineStr">
         <is>
@@ -67702,17 +67610,17 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -67737,7 +67645,7 @@
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -67746,81 +67654,173 @@
         </is>
       </c>
       <c r="N373" t="n">
+        <v>0</v>
+      </c>
+      <c r="O373" t="n">
+        <v>0</v>
+      </c>
+      <c r="P373" t="n">
+        <v>0</v>
+      </c>
+      <c r="U373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W373" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X373" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y373" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA373" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB373" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC373" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD373" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE373" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF373" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG373" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH373" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI373" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ373" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM373" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN373" t="b">
         <v>1</v>
       </c>
-      <c r="O373" t="n">
-        <v>1</v>
-      </c>
-      <c r="R373" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S373" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP373" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR373" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS373" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ373" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS373" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU373" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV373" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW373" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX373" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY373" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ373" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA373" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB373" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC373" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -67852,12 +67852,12 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -67882,7 +67882,7 @@
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -67891,13 +67891,13 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="O374" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="R374" t="n">
-        <v>0.05962701375230094</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S374" t="inlineStr">
         <is>
@@ -67930,42 +67930,42 @@
       </c>
       <c r="AV374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ374" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA374" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB374" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC374" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -67997,12 +67997,12 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -68036,93 +68036,81 @@
         </is>
       </c>
       <c r="N375" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="O375" t="n">
-        <v>4</v>
-      </c>
-      <c r="P375" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="R375" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.05962701375230094</v>
       </c>
       <c r="S375" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO375" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP375" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ375" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS375" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR375" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS375" t="inlineStr"/>
       <c r="AT375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU375" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ375" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA375" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB375" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC375" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68149,7 +68137,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -68201,98 +68189,18 @@
       <c r="P376" t="n">
         <v>4</v>
       </c>
-      <c r="U376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W376" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X376" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y376" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R376" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB376" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC376" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD376" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE376" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF376" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG376" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH376" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI376" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ376" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK376" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM376" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN376" t="b">
-        <v>1</v>
       </c>
       <c r="AO376" t="inlineStr">
         <is>
@@ -68386,17 +68294,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -68421,7 +68329,7 @@
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
@@ -68430,81 +68338,173 @@
         </is>
       </c>
       <c r="N377" t="n">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="O377" t="n">
-        <v>64</v>
-      </c>
-      <c r="R377" t="n">
-        <v>0.05227573808420904</v>
-      </c>
-      <c r="S377" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P377" t="n">
+        <v>4</v>
+      </c>
+      <c r="U377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA377" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB377" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC377" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF377" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG377" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH377" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI377" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ377" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM377" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN377" t="b">
+        <v>1</v>
       </c>
       <c r="AO377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP377" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR377" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS377" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ377" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS377" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU377" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ377" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA377" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB377" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC377" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -68536,12 +68536,12 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -68575,93 +68575,81 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="O378" t="n">
-        <v>3</v>
-      </c>
-      <c r="P378" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="R378" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.05227573808420904</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA378" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO378" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP378" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ378" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS378" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR378" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS378" t="inlineStr"/>
       <c r="AT378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU378" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ378" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA378" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB378" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC378" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -68688,7 +68676,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -68740,98 +68728,18 @@
       <c r="P379" t="n">
         <v>3</v>
       </c>
-      <c r="U379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W379" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X379" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y379" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R379" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB379" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC379" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD379" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE379" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF379" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG379" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH379" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI379" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ379" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK379" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM379" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN379" t="b">
-        <v>1</v>
       </c>
       <c r="AO379" t="inlineStr">
         <is>
@@ -68925,17 +68833,17 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -68960,7 +68868,7 @@
       </c>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
@@ -68969,81 +68877,173 @@
         </is>
       </c>
       <c r="N380" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
       <c r="O380" t="n">
-        <v>91</v>
-      </c>
-      <c r="R380" t="n">
-        <v>0.07432956508848473</v>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P380" t="n">
+        <v>3</v>
+      </c>
+      <c r="U380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA380" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB380" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC380" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF380" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG380" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH380" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI380" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ380" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM380" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN380" t="b">
+        <v>1</v>
       </c>
       <c r="AO380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP380" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR380" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS380" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ380" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS380" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT380" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU380" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV380" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW380" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX380" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY380" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ380" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA380" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB380" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC380" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69075,12 +69075,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -69114,93 +69114,81 @@
         </is>
       </c>
       <c r="N381" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="O381" t="n">
-        <v>4</v>
-      </c>
-      <c r="P381" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="R381" t="n">
-        <v>0.0677306302038819</v>
+        <v>0.07432956508848473</v>
       </c>
       <c r="S381" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA381" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO381" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP381" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ381" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS381" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR381" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS381" t="inlineStr"/>
       <c r="AT381" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU381" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV381" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW381" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX381" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY381" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ381" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA381" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB381" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC381" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69227,7 +69215,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -69279,98 +69267,18 @@
       <c r="P382" t="n">
         <v>4</v>
       </c>
-      <c r="U382" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W382" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X382" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y382" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z382" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R382" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB382" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC382" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD382" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE382" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF382" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG382" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH382" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI382" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ382" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK382" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM382" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN382" t="b">
-        <v>1</v>
       </c>
       <c r="AO382" t="inlineStr">
         <is>
@@ -69464,17 +69372,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -69499,7 +69407,7 @@
       </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
@@ -69508,81 +69416,173 @@
         </is>
       </c>
       <c r="N383" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="O383" t="n">
-        <v>110</v>
-      </c>
-      <c r="R383" t="n">
-        <v>0.08984892483223429</v>
-      </c>
-      <c r="S383" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="P383" t="n">
+        <v>4</v>
+      </c>
+      <c r="U383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z383" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF383" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG383" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH383" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI383" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ383" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK383" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM383" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN383" t="b">
+        <v>1</v>
       </c>
       <c r="AO383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP383" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR383" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS383" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ383" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS383" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU383" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ383" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA383" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB383" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC383" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -69614,12 +69614,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -69653,93 +69653,81 @@
         </is>
       </c>
       <c r="N384" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="O384" t="n">
-        <v>2</v>
-      </c>
-      <c r="P384" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="R384" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.08984892483223429</v>
       </c>
       <c r="S384" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA384" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO384" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP384" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ384" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS384" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR384" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS384" t="inlineStr"/>
       <c r="AT384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU384" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV384" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW384" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX384" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY384" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ384" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA384" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB384" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC384" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -69766,7 +69754,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -69818,98 +69806,18 @@
       <c r="P385" t="n">
         <v>2</v>
       </c>
-      <c r="U385" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W385" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X385" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y385" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R385" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB385" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC385" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD385" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE385" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF385" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG385" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH385" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI385" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ385" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK385" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM385" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN385" t="b">
-        <v>1</v>
       </c>
       <c r="AO385" t="inlineStr">
         <is>
@@ -70003,17 +69911,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -70038,12 +69946,12 @@
       </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N386" t="n">
@@ -70052,76 +69960,168 @@
       <c r="O386" t="n">
         <v>2</v>
       </c>
-      <c r="R386" t="n">
-        <v>0.007345623639039581</v>
-      </c>
-      <c r="S386" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P386" t="n">
+        <v>2</v>
+      </c>
+      <c r="U386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF386" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG386" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH386" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI386" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ386" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM386" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN386" t="b">
+        <v>1</v>
       </c>
       <c r="AO386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP386" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR386" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS386" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ386" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS386" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
       <c r="AT386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU386" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV386" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW386" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX386" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY386" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ386" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA386" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB386" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC386" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -70153,12 +70153,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -70192,100 +70192,81 @@
         </is>
       </c>
       <c r="N387" t="n">
+        <v>2</v>
+      </c>
+      <c r="O387" t="n">
+        <v>2</v>
+      </c>
+      <c r="R387" t="n">
+        <v>0.007345623639039581</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO387" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP387" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR387" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS387" t="inlineStr"/>
+      <c r="AT387" t="n">
         <v>0</v>
       </c>
-      <c r="O387" t="n">
-        <v>0</v>
-      </c>
-      <c r="R387" t="n">
-        <v>0</v>
-      </c>
-      <c r="S387" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U387" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO387" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP387" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ387" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR387" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS387" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="AT387" t="n">
-        <v>2</v>
-      </c>
       <c r="AU387" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV387" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW387" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX387" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY387" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ387" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA387" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB387" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC387" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -70312,7 +70293,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -70361,98 +70342,23 @@
       <c r="O388" t="n">
         <v>0</v>
       </c>
+      <c r="R388" t="n">
+        <v>0</v>
+      </c>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U388" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_171</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_171</t>
-        </is>
-      </c>
-      <c r="W388" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X388" t="inlineStr">
-        <is>
-          <t>Swine fever</t>
-        </is>
-      </c>
-      <c r="Y388" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z388" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA388" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB388" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC388" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD388" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE388" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF388" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG388" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH388" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI388" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ388" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK388" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
-        </is>
-      </c>
-      <c r="AM388" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN388" t="b">
-        <v>1</v>
       </c>
       <c r="AO388" t="inlineStr">
         <is>
@@ -70551,17 +70457,17 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -70595,81 +70501,175 @@
         </is>
       </c>
       <c r="N389" t="n">
-        <v>264</v>
+        <v>0</v>
       </c>
       <c r="O389" t="n">
-        <v>264</v>
-      </c>
-      <c r="R389" t="n">
-        <v>0.5116240598811002</v>
-      </c>
-      <c r="S389" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U389" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF389" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG389" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH389" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI389" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ389" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM389" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN389" t="b">
+        <v>1</v>
       </c>
       <c r="AO389" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP389" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ389" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR389" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS389" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS389" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
       <c r="AT389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU389" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV389" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW389" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ389" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA389" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB389" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC389" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -70701,12 +70701,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -70740,100 +70740,81 @@
         </is>
       </c>
       <c r="N390" t="n">
+        <v>297</v>
+      </c>
+      <c r="O390" t="n">
+        <v>297</v>
+      </c>
+      <c r="R390" t="n">
+        <v>0.5755770673662376</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP390" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR390" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS390" t="inlineStr"/>
+      <c r="AT390" t="n">
         <v>0</v>
       </c>
-      <c r="O390" t="n">
-        <v>0</v>
-      </c>
-      <c r="R390" t="n">
-        <v>0</v>
-      </c>
-      <c r="S390" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U390" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA390" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO390" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP390" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ390" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR390" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS390" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT390" t="n">
-        <v>2</v>
-      </c>
       <c r="AU390" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV390" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW390" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX390" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY390" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ390" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA390" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB390" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC390" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -70860,7 +70841,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -70909,98 +70890,23 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
+      <c r="R391" t="n">
+        <v>0</v>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U391" t="inlineStr">
         <is>
           <t>SER_NO_FHI_105_MONTHLY</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_105_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W391" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X391" t="inlineStr">
-        <is>
-          <t>Kusma</t>
-        </is>
-      </c>
-      <c r="Y391" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z391" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA391" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB391" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC391" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD391" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE391" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF391" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG391" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH391" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI391" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ391" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK391" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM391" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN391" t="b">
-        <v>1</v>
       </c>
       <c r="AO391" t="inlineStr">
         <is>
@@ -71099,17 +71005,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -71134,7 +71040,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -71143,81 +71049,175 @@
         </is>
       </c>
       <c r="N392" t="n">
+        <v>0</v>
+      </c>
+      <c r="O392" t="n">
+        <v>0</v>
+      </c>
+      <c r="U392" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>Kusma</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF392" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG392" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH392" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI392" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ392" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK392" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM392" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN392" t="b">
         <v>1</v>
       </c>
-      <c r="O392" t="n">
-        <v>1</v>
-      </c>
-      <c r="R392" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S392" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO392" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP392" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ392" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR392" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS392" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS392" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_105_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT392" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU392" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV392" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW392" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX392" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY392" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ392" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA392" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB392" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC392" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -71249,12 +71249,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -71279,7 +71279,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
@@ -71288,13 +71288,13 @@
         </is>
       </c>
       <c r="N393" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O393" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="R393" t="n">
-        <v>0.05881020534473518</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S393" t="inlineStr">
         <is>
@@ -71327,42 +71327,42 @@
       </c>
       <c r="AV393" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW393" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX393" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY393" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ393" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA393" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB393" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC393" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -71394,12 +71394,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -71433,93 +71433,81 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="O394" t="n">
-        <v>2</v>
-      </c>
-      <c r="P394" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="R394" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05881020534473518</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA394" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO394" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP394" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ394" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS394" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR394" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS394" t="inlineStr"/>
       <c r="AT394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU394" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV394" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW394" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX394" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY394" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ394" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA394" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB394" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC394" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -71546,7 +71534,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -71598,98 +71586,18 @@
       <c r="P395" t="n">
         <v>2</v>
       </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="V395" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MUMPS</t>
-        </is>
-      </c>
-      <c r="W395" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X395" t="inlineStr">
-        <is>
-          <t>Mumps</t>
-        </is>
-      </c>
-      <c r="Y395" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z395" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R395" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA395" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB395" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC395" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD395" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE395" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF395" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG395" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH395" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI395" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ395" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK395" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM395" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN395" t="b">
-        <v>1</v>
       </c>
       <c r="AO395" t="inlineStr">
         <is>
@@ -71757,6 +71665,927 @@
       <c r="BC395" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N396" t="n">
+        <v>2</v>
+      </c>
+      <c r="O396" t="n">
+        <v>2</v>
+      </c>
+      <c r="P396" t="n">
+        <v>2</v>
+      </c>
+      <c r="U396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB396" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC396" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF396" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG396" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH396" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI396" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ396" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM396" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN396" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO396" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP396" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ396" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS396" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT396" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU396" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV396" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW396" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX396" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY396" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA396" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB396" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC396" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>114</v>
+      </c>
+      <c r="O397" t="n">
+        <v>114</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0.09311615846249736</v>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR397" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr"/>
+      <c r="AT397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU397" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW397" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX397" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA397" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB397" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC397" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N398" t="n">
+        <v>5</v>
+      </c>
+      <c r="O398" t="n">
+        <v>5</v>
+      </c>
+      <c r="P398" t="n">
+        <v>5</v>
+      </c>
+      <c r="R398" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO398" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP398" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ398" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS398" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT398" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU398" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV398" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW398" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX398" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY398" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA398" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB398" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC398" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N399" t="n">
+        <v>5</v>
+      </c>
+      <c r="O399" t="n">
+        <v>5</v>
+      </c>
+      <c r="P399" t="n">
+        <v>5</v>
+      </c>
+      <c r="U399" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB399" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC399" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF399" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG399" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH399" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI399" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ399" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM399" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN399" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO399" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP399" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ399" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS399" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT399" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU399" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV399" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW399" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX399" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY399" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA399" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB399" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC399" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N400" t="n">
+        <v>3</v>
+      </c>
+      <c r="O400" t="n">
+        <v>3</v>
+      </c>
+      <c r="R400" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP400" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR400" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS400" t="inlineStr"/>
+      <c r="AT400" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU400" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV400" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW400" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX400" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY400" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA400" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB400" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC400" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -71793,7 +72622,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -71876,7 +72705,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10">
@@ -71886,7 +72715,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11">
@@ -71906,7 +72735,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -71938,7 +72767,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72926</v>
+        <v>73086</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -68943,13 +68943,13 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O379" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="R379" t="n">
-        <v>0.8197612777640354</v>
+        <v>0.8216992476878274</v>
       </c>
       <c r="S379" t="inlineStr">
         <is>
@@ -73272,13 +73272,13 @@
         </is>
       </c>
       <c r="N403" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O403" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R403" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.01469124727807916</v>
       </c>
       <c r="S403" t="inlineStr">
         <is>
@@ -73820,13 +73820,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="O406" t="n">
-        <v>297</v>
+        <v>368</v>
       </c>
       <c r="R406" t="n">
-        <v>0.5755770673662376</v>
+        <v>0.7131729319554728</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -75666,6 +75666,1238 @@
       <c r="BC416" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N417" t="n">
+        <v>96</v>
+      </c>
+      <c r="O417" t="n">
+        <v>96</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0.07841360712631357</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO417" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP417" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr"/>
+      <c r="AT417" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU417" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV417" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW417" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX417" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY417" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA417" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB417" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC417" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N418" t="n">
+        <v>6</v>
+      </c>
+      <c r="O418" t="n">
+        <v>6</v>
+      </c>
+      <c r="P418" t="n">
+        <v>6</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0.1015959453058228</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO418" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP418" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ418" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT418" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU418" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV418" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW418" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX418" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY418" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA418" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB418" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC418" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N419" t="n">
+        <v>6</v>
+      </c>
+      <c r="O419" t="n">
+        <v>6</v>
+      </c>
+      <c r="P419" t="n">
+        <v>6</v>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB419" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC419" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD419" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE419" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF419" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG419" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH419" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI419" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ419" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK419" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM419" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN419" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO419" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP419" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ419" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS419" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MUMPS; SER_SG_HIST_MUMPS</t>
+        </is>
+      </c>
+      <c r="AT419" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU419" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV419" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW419" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX419" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY419" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA419" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB419" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC419" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N420" t="n">
+        <v>2</v>
+      </c>
+      <c r="O420" t="n">
+        <v>2</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO420" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP420" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR420" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr"/>
+      <c r="AT420" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU420" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV420" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW420" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX420" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY420" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA420" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB420" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC420" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N421" t="n">
+        <v>0</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0</v>
+      </c>
+      <c r="R421" t="n">
+        <v>0</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO421" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP421" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ421" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR421" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AT421" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU421" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV421" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW421" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX421" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY421" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA421" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB421" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC421" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N422" t="n">
+        <v>0</v>
+      </c>
+      <c r="O422" t="n">
+        <v>0</v>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>Swine fever</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB422" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC422" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD422" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE422" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG422" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI422" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ422" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; The English cube mistranslates Finnish Sikotauti; source code 171 is mumps.</t>
+        </is>
+      </c>
+      <c r="AM422" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN422" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO422" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP422" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ422" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_171</t>
+        </is>
+      </c>
+      <c r="AT422" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU422" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV422" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW422" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX422" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY422" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA422" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB422" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC422" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N423" t="n">
+        <v>5</v>
+      </c>
+      <c r="O423" t="n">
+        <v>5</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0.009689849618960231</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO423" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP423" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR423" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr"/>
+      <c r="AT423" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU423" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV423" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW423" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX423" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY423" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA423" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB423" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC423" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -75702,7 +76934,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -75785,7 +77017,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10">
@@ -75795,7 +77027,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>415</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11">
@@ -75815,7 +77047,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -75847,7 +77079,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75066</v>
+        <v>75249</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -5860,7 +5860,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -14962,7 +14962,7 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN79" t="b">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -32343,7 +32343,7 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN174" t="b">
@@ -41143,7 +41143,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="AM278" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN278" t="b">
@@ -60731,7 +60731,7 @@
       </c>
       <c r="AM332" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN332" t="b">
@@ -69344,7 +69344,7 @@
       </c>
       <c r="AM381" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN381" t="b">
@@ -74221,7 +74221,7 @@
       </c>
       <c r="AM408" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN408" t="b">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -81621,13 +81621,13 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O461" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R461" t="n">
-        <v>0.7480563905837297</v>
+        <v>0.7499943605075218</v>
       </c>
       <c r="S461" t="inlineStr">
         <is>
@@ -84769,13 +84769,13 @@
         </is>
       </c>
       <c r="N479" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O479" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="R479" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.07751879695168185</v>
       </c>
       <c r="S479" t="inlineStr">
         <is>
@@ -85025,7 +85025,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75393</v>
+        <v>75400</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -82696,13 +82696,13 @@
         </is>
       </c>
       <c r="N463" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="O463" t="n">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="R463" t="n">
-        <v>0.7519323304313138</v>
+        <v>0.7558082702788979</v>
       </c>
       <c r="S463" t="inlineStr">
         <is>
@@ -86661,13 +86661,13 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="O485" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="R485" t="n">
-        <v>0.1124022555799387</v>
+        <v>0.1918590224554125</v>
       </c>
       <c r="S485" t="inlineStr">
         <is>
@@ -87475,7 +87475,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75428</v>
+        <v>75471</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -83249,13 +83249,13 @@
         </is>
       </c>
       <c r="N466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O466" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R466" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S466" t="inlineStr">
         <is>
@@ -83413,10 +83413,10 @@
         </is>
       </c>
       <c r="N467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O467" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U467" t="inlineStr">
         <is>
@@ -86661,13 +86661,13 @@
         </is>
       </c>
       <c r="N485" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="O485" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="R485" t="n">
-        <v>0.1918590224554125</v>
+        <v>0.2306184209312535</v>
       </c>
       <c r="S485" t="inlineStr">
         <is>
@@ -87294,6 +87294,151 @@
       <c r="BC488" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>mumps</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>D039</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Mumps</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>流行性腮腺炎</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N489" t="n">
+        <v>107</v>
+      </c>
+      <c r="O489" t="n">
+        <v>107</v>
+      </c>
+      <c r="R489" t="n">
+        <v>0.08739849960953699</v>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO489" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP489" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR489" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS489" t="inlineStr"/>
+      <c r="AT489" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU489" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV489" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW489" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX489" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY489" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA489" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB489" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC489" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -87330,7 +87475,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -87413,7 +87558,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -87423,7 +87568,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11">
@@ -87475,7 +87620,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75471</v>
+        <v>75597</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d039/2026-2029.xlsx
+++ b/diseases/d039/2026-2029.xlsx
@@ -7605,13 +7605,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -8856,9 +8856,6 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -9551,9 +9548,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -10246,9 +10240,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -10941,9 +10932,6 @@
       <c r="O59" t="n">
         <v>3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -18857,9 +18845,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -19552,9 +19537,6 @@
       <c r="O107" t="n">
         <v>7</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.00200552669293857</v>
       </c>
@@ -20247,9 +20229,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -20942,9 +20921,6 @@
       <c r="O115" t="n">
         <v>6</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.001719022879661631</v>
       </c>
@@ -28648,9 +28624,6 @@
       <c r="O158" t="n">
         <v>3</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -30038,9 +30011,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -38267,9 +38237,6 @@
       <c r="O212" t="n">
         <v>2</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -39657,9 +39624,6 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -40352,9 +40316,6 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -49120,9 +49081,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -49814,9 +49772,6 @@
       </c>
       <c r="O277" t="n">
         <v>2</v>
-      </c>
-      <c r="Q277" t="n">
-        <v>0</v>
       </c>
       <c r="R277" t="n">
         <v>0.0005730076265538771</v>
@@ -87620,7 +87575,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75597</v>
+        <v>75596</v>
       </c>
     </row>
     <row r="16">
